--- a/TestData/ddt.xlsx
+++ b/TestData/ddt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="7200" yWindow="4095" windowWidth="21600" windowHeight="11385" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="credentials" sheetId="1" state="visible" r:id="rId1"/>
@@ -425,11 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.42578125" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13.5703125" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,6 +454,11 @@
           <t>Actual</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Error message</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,7 +478,12 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Invalid credentials</t>
         </is>
       </c>
     </row>
@@ -516,7 +527,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Invalid credentials</t>
         </is>
       </c>
     </row>
@@ -538,7 +554,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Invalid credentials</t>
         </is>
       </c>
     </row>
@@ -582,7 +603,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Invalid credentials</t>
         </is>
       </c>
     </row>
